--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484343_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484343_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9407</v>
+        <v>3.4251</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9169</v>
+        <v>5.483</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.9762</v>
+        <v>-2.0579</v>
       </c>
       <c r="G2" t="n">
         <v>1.3185</v>
@@ -610,13 +610,13 @@
         <v>2.5395</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.3146</v>
+        <v>-0.8302</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0151</v>
+        <v>-0.449</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2995</v>
+        <v>-0.3812</v>
       </c>
       <c r="V2" t="n">
         <v>1.374</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3647</v>
+        <v>0.2035</v>
       </c>
       <c r="E3" t="n">
-        <v>4.062</v>
+        <v>3.8192</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.6973</v>
+        <v>-3.6156</v>
       </c>
       <c r="G3" t="n">
         <v>-3.5377</v>
@@ -688,13 +688,13 @@
         <v>2.3441</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.2111</v>
+        <v>-1.3722</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4153</v>
+        <v>-0.6581</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7958</v>
+        <v>-0.7141</v>
       </c>
       <c r="V3" t="n">
         <v>2.7693</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. CALLAVE FERRER</t>
+          <t>R. NOGUER SANTAELLA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0568</v>
+        <v>0.1205</v>
       </c>
       <c r="E4" t="n">
-        <v>0.325</v>
+        <v>-0.9629</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3818</v>
+        <v>1.0834</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1643</v>
+        <v>-2.0391</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.7127</v>
+        <v>-1.1087</v>
       </c>
       <c r="I4" t="n">
-        <v>0.877</v>
+        <v>-0.9303</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9981</v>
+        <v>-0.3316</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3901</v>
+        <v>0.3287</v>
       </c>
       <c r="L4" t="n">
-        <v>0.608</v>
+        <v>-0.6603</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8338</v>
+        <v>-1.7075</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1028</v>
+        <v>-1.4375</v>
       </c>
       <c r="O4" t="n">
-        <v>0.269</v>
+        <v>-0.27</v>
       </c>
       <c r="P4" t="n">
         <v>1.3674</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3441</v>
+        <v>1.3674</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9707</v>
+        <v>-1.0785</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6357</v>
+        <v>-0.6313</v>
       </c>
       <c r="U4" t="n">
-        <v>0.335</v>
+        <v>-0.4471</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.5591</v>
+        <v>1.8706</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.227</v>
+        <v>1.8706</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. NOGUER SANTAELLA</t>
+          <t>J. CALLAVE FERRER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2784</v>
+        <v>-0.5507</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.2256</v>
+        <v>0.0217</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9472</v>
+        <v>-0.5724</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.0391</v>
+        <v>0.1643</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.1087</v>
+        <v>-0.7127</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9303</v>
+        <v>0.877</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.3316</v>
+        <v>0.9981</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3287</v>
+        <v>0.3901</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6603</v>
+        <v>0.608</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.7075</v>
+        <v>-0.8338</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4375</v>
+        <v>-1.1028</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.27</v>
+        <v>0.269</v>
       </c>
       <c r="P5" t="n">
         <v>1.3674</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3674</v>
+        <v>2.3441</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.4774</v>
+        <v>0.4767</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8941</v>
+        <v>0.3324</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5833</v>
+        <v>0.1443</v>
       </c>
       <c r="V5" t="n">
-        <v>1.8706</v>
+        <v>-2.5591</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X5" t="n">
-        <v>1.8706</v>
+        <v>-2.227</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.2676</v>
+        <v>-2.0238</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1345</v>
+        <v>-1.7818</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.133</v>
+        <v>-0.242</v>
       </c>
       <c r="G6" t="n">
         <v>-0.0039</v>
@@ -922,13 +922,13 @@
         <v>1.9534</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0451</v>
+        <v>-0.8013</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3331</v>
+        <v>-0.3142</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3782</v>
+        <v>-0.4871</v>
       </c>
       <c r="V6" t="n">
         <v>-1.2186</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.1412</v>
+        <v>-2.4528</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.424</v>
+        <v>-0.8173</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7172</v>
+        <v>-1.6355</v>
       </c>
       <c r="G7" t="n">
         <v>1.3427</v>
@@ -1000,13 +1000,13 @@
         <v>3.1255</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.7174</v>
+        <v>-1.029</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0894</v>
+        <v>-0.4827</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.628</v>
+        <v>-0.5463</v>
       </c>
       <c r="V7" t="n">
         <v>-1.0084</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. MONTSERRAT SERRA</t>
+          <t>M. SERRAT PONCE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.7316</v>
+        <v>-2.7142</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9263</v>
+        <v>-1.7929</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.8053</v>
+        <v>-0.9213</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.0885</v>
+        <v>-3.1127</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.0115</v>
+        <v>-3.0578</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.077</v>
+        <v>-0.0549</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.6318</v>
+        <v>-0.9807</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3646</v>
+        <v>-1.0617</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2673</v>
+        <v>0.0809</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.4567</v>
+        <v>-2.132</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.647</v>
+        <v>-1.9962</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8097</v>
+        <v>-0.1358</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3674</v>
+        <v>3.3208</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3441</v>
+        <v>3.3208</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8885999999999999</v>
+        <v>-1.7037</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5364</v>
+        <v>-0.8122</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3523</v>
+        <v>-0.8915999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1219</v>
+        <v>-1.2186</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.3405</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. SERRAT PONCE</t>
+          <t>M. MONTSERRAT SERRA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.7766</v>
+        <v>-4.1863</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4195</v>
+        <v>-2.1086</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3571</v>
+        <v>-2.0777</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.1127</v>
+        <v>-4.0885</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.0578</v>
+        <v>-2.0115</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0549</v>
+        <v>-2.077</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9807</v>
+        <v>-1.6318</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.0617</v>
+        <v>-0.3646</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0809</v>
+        <v>-1.2673</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.132</v>
+        <v>-2.4567</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.9962</v>
+        <v>-1.647</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1358</v>
+        <v>-0.8097</v>
       </c>
       <c r="P9" t="n">
-        <v>3.3208</v>
+        <v>1.3674</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R9" t="n">
-        <v>3.3208</v>
+        <v>2.3441</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.7661</v>
+        <v>-1.3433</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.4388</v>
+        <v>-0.7187</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.3273</v>
+        <v>-0.6246</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2186</v>
+        <v>-0.1219</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2186</v>
+        <v>-1.3405</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.2206</v>
+        <v>-7.3835</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.6594</v>
+        <v>-5.7406</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5612</v>
+        <v>-1.6429</v>
       </c>
       <c r="G10" t="n">
         <v>-6.6684</v>
@@ -1234,13 +1234,13 @@
         <v>2.1488</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5057</v>
+        <v>-0.6686</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4758</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0298</v>
+        <v>-0.1116</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2186</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-16.1674</v>
+        <v>-15.5622</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.485400000000002</v>
+        <v>-3.880200000000001</v>
       </c>
       <c r="F11" t="n">
         <v>-11.6819</v>
@@ -1312,13 +1312,13 @@
         <v>21.4877</v>
       </c>
       <c r="S11" t="n">
-        <v>-8.955300000000001</v>
+        <v>-8.350099999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-4.896100000000001</v>
+        <v>-4.2908</v>
       </c>
       <c r="U11" t="n">
-        <v>-4.0592</v>
+        <v>-4.059299999999999</v>
       </c>
       <c r="V11" t="n">
         <v>-1.3313</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. GARCÍA RIERA</t>
+          <t>J. HERNANDEZ GIMENEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.870900000000001</v>
+        <v>8.9512</v>
       </c>
       <c r="E12" t="n">
-        <v>5.3532</v>
+        <v>7.7284</v>
       </c>
       <c r="F12" t="n">
-        <v>4.5177</v>
+        <v>1.2228</v>
       </c>
       <c r="G12" t="n">
-        <v>1.497</v>
+        <v>7.7903</v>
       </c>
       <c r="H12" t="n">
-        <v>2.0898</v>
+        <v>4.5529</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5928</v>
+        <v>3.2375</v>
       </c>
       <c r="J12" t="n">
-        <v>1.118</v>
+        <v>7.6158</v>
       </c>
       <c r="K12" t="n">
-        <v>1.8445</v>
+        <v>4.647</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.7264</v>
+        <v>2.9688</v>
       </c>
       <c r="M12" t="n">
-        <v>0.379</v>
+        <v>0.1745</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2454</v>
+        <v>-0.0941</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1336</v>
+        <v>0.2687</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.3907</v>
+        <v>-0.586</v>
       </c>
       <c r="Q12" t="n">
         <v>-2.1488</v>
       </c>
       <c r="R12" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="S12" t="n">
-        <v>4.4993</v>
+        <v>1.1376</v>
       </c>
       <c r="T12" t="n">
-        <v>2.1187</v>
+        <v>0.4335</v>
       </c>
       <c r="U12" t="n">
-        <v>2.3806</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>4.2652</v>
+        <v>0.6093</v>
       </c>
       <c r="W12" t="n">
-        <v>4.2652</v>
+        <v>1.8279</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>V. MARKOVETSKYY</t>
+          <t>G. GARCÍA RIERA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.718500000000001</v>
+        <v>8.3188</v>
       </c>
       <c r="E13" t="n">
-        <v>6.1079</v>
+        <v>4.6454</v>
       </c>
       <c r="F13" t="n">
-        <v>2.6106</v>
+        <v>3.6734</v>
       </c>
       <c r="G13" t="n">
-        <v>5.5305</v>
+        <v>1.497</v>
       </c>
       <c r="H13" t="n">
-        <v>4.6951</v>
+        <v>2.0898</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8354</v>
+        <v>-0.5928</v>
       </c>
       <c r="J13" t="n">
-        <v>4.6067</v>
+        <v>1.118</v>
       </c>
       <c r="K13" t="n">
-        <v>4.4449</v>
+        <v>1.8445</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1619</v>
+        <v>-0.7264</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9237</v>
+        <v>0.379</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2502</v>
+        <v>0.2454</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6735</v>
+        <v>0.1336</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.9767</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9534</v>
+        <v>-2.1488</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9767</v>
+        <v>1.7581</v>
       </c>
       <c r="S13" t="n">
-        <v>3.6103</v>
+        <v>2.9473</v>
       </c>
       <c r="T13" t="n">
-        <v>2.9001</v>
+        <v>1.4109</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7102000000000001</v>
+        <v>1.5363</v>
       </c>
       <c r="V13" t="n">
-        <v>0.5545</v>
+        <v>4.2652</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5545</v>
+        <v>4.2652</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. HERNANDEZ GIMENEZ</t>
+          <t>V. MARKOVETSKYY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.6133</v>
+        <v>7.1201</v>
       </c>
       <c r="E14" t="n">
-        <v>6.7173</v>
+        <v>4.5911</v>
       </c>
       <c r="F14" t="n">
-        <v>0.896</v>
+        <v>2.5289</v>
       </c>
       <c r="G14" t="n">
-        <v>7.7903</v>
+        <v>5.5305</v>
       </c>
       <c r="H14" t="n">
-        <v>4.5529</v>
+        <v>4.6951</v>
       </c>
       <c r="I14" t="n">
-        <v>3.2375</v>
+        <v>0.8354</v>
       </c>
       <c r="J14" t="n">
-        <v>7.6158</v>
+        <v>4.6067</v>
       </c>
       <c r="K14" t="n">
-        <v>4.647</v>
+        <v>4.4449</v>
       </c>
       <c r="L14" t="n">
-        <v>2.9688</v>
+        <v>0.1619</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1745</v>
+        <v>0.9237</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0941</v>
+        <v>0.2502</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2687</v>
+        <v>0.6735</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.586</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.1488</v>
+        <v>-1.9534</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5627</v>
+        <v>0.9767</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2004</v>
+        <v>2.0119</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5777</v>
+        <v>1.3834</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3773</v>
+        <v>0.6284999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6093</v>
+        <v>0.5545</v>
       </c>
       <c r="W14" t="n">
-        <v>1.8279</v>
+        <v>0.5545</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6766</v>
+        <v>2.5003</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2748</v>
+        <v>1.0726</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4018</v>
+        <v>1.4277</v>
       </c>
       <c r="G15" t="n">
         <v>-1.5123</v>
@@ -1624,13 +1624,13 @@
         <v>1.3674</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4158</v>
+        <v>1.2395</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8173</v>
+        <v>0.615</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5985</v>
+        <v>0.6244</v>
       </c>
       <c r="V15" t="n">
         <v>2.3824</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0725</v>
+        <v>0.3929</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0578</v>
+        <v>0.2456</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0147</v>
+        <v>0.1474</v>
       </c>
       <c r="G16" t="n">
         <v>0.3742</v>
@@ -1702,13 +1702,13 @@
         <v>0.9767</v>
       </c>
       <c r="S16" t="n">
-        <v>0.772</v>
+        <v>1.2374</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3247</v>
+        <v>0.6281</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4472</v>
+        <v>0.6093</v>
       </c>
       <c r="V16" t="n">
         <v>-1.2186</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.703</v>
+        <v>0.2836</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6692</v>
+        <v>1.2759</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3722</v>
+        <v>-0.9923</v>
       </c>
       <c r="G17" t="n">
         <v>2.2237</v>
@@ -1780,13 +1780,13 @@
         <v>1.1721</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.204</v>
+        <v>-0.2174</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8473000000000001</v>
+        <v>-0.2406</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3567</v>
+        <v>0.0233</v>
       </c>
       <c r="V17" t="n">
         <v>-0.9414</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.1797</v>
+        <v>-1.285</v>
       </c>
       <c r="E18" t="n">
-        <v>-4.2607</v>
+        <v>-3.8562</v>
       </c>
       <c r="F18" t="n">
-        <v>2.081</v>
+        <v>2.5712</v>
       </c>
       <c r="G18" t="n">
         <v>1.6873</v>
@@ -1858,13 +1858,13 @@
         <v>1.1721</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2922</v>
+        <v>0.6025</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4099</v>
+        <v>-0.0054</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1177</v>
+        <v>0.6079</v>
       </c>
       <c r="V18" t="n">
         <v>0.3321</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.2505</v>
+        <v>-3.9989</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.5365</v>
+        <v>-2.6376</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.714</v>
+        <v>-1.3613</v>
       </c>
       <c r="G19" t="n">
         <v>-1.4074</v>
@@ -1936,13 +1936,13 @@
         <v>0.9767</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2471</v>
+        <v>0.4987</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1432</v>
+        <v>0.0421</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1039</v>
+        <v>0.4566</v>
       </c>
       <c r="V19" t="n">
         <v>-0.9414</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.5062</v>
+        <v>-5.4415</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5855</v>
+        <v>-1.3833</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.9207</v>
+        <v>-4.0583</v>
       </c>
       <c r="G20" t="n">
         <v>0.4414</v>
@@ -2014,13 +2014,13 @@
         <v>0.7814</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1073</v>
+        <v>0.172</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4099</v>
+        <v>-0.2077</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5172</v>
+        <v>0.3796</v>
       </c>
       <c r="V20" t="n">
         <v>-3.7107</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>16.1674</v>
+        <v>16.8415</v>
       </c>
       <c r="E21" t="n">
         <v>11.6819</v>
       </c>
       <c r="F21" t="n">
-        <v>4.4855</v>
+        <v>5.1595</v>
       </c>
       <c r="G21" t="n">
         <v>16.6247</v>
@@ -2092,16 +2092,16 @@
         <v>10.7439</v>
       </c>
       <c r="S21" t="n">
-        <v>8.955200000000001</v>
+        <v>9.6295</v>
       </c>
       <c r="T21" t="n">
-        <v>4.059200000000001</v>
+        <v>4.0593</v>
       </c>
       <c r="U21" t="n">
-        <v>4.895899999999999</v>
+        <v>5.57</v>
       </c>
       <c r="V21" t="n">
-        <v>1.331399999999999</v>
+        <v>1.3314</v>
       </c>
       <c r="W21" t="n">
         <v>11.6348</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484343_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484343_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X21"/>
+  <dimension ref="A1:Y21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.3405</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484343_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-2.1052</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484343_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>1.8706</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484343_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-2.227</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484343_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484343_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-2.8364</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484343_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484343_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.3405</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484343_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484343_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,7 @@
       <c r="X11" t="n">
         <v>-11.6348</v>
       </c>
+      <c r="Y11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,11 +1458,16 @@
       <c r="X12" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484343_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>G. GARCÍA RIERA</t>
+          <t>G. GARCIA RIERA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1484,6 +1540,11 @@
       </c>
       <c r="X13" t="n">
         <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484343_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484343_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.6093</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484343_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484343_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-2.4373</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484343_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0.3321</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484343_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.4959</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484343_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-3.6559</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484343_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,7 @@
       <c r="X21" t="n">
         <v>-10.3035</v>
       </c>
+      <c r="Y21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
